--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +891,7 @@
         <v>126982560</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126981219</v>
+        <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467207</v>
+        <v>467099</v>
       </c>
       <c r="R6" t="n">
-        <v>6788653</v>
+        <v>6788291</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126982281</v>
+        <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467099</v>
+        <v>467207</v>
       </c>
       <c r="R7" t="n">
-        <v>6788291</v>
+        <v>6788653</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,7 +1423,7 @@
         <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>126981689</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>80043</v>
+        <v>80074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R12" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126982112</v>
+        <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467212</v>
+        <v>467015</v>
       </c>
       <c r="R13" t="n">
-        <v>6788366</v>
+        <v>6788576</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126981571</v>
+        <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467237</v>
+        <v>467048</v>
       </c>
       <c r="R17" t="n">
-        <v>6788467</v>
+        <v>6788349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,43 +2376,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126980955</v>
+        <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2420,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466936</v>
+        <v>467237</v>
       </c>
       <c r="R18" t="n">
-        <v>6788497</v>
+        <v>6788467</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2456,6 +2450,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,37 +2482,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126982391</v>
+        <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467048</v>
+        <v>466936</v>
       </c>
       <c r="R19" t="n">
-        <v>6788349</v>
+        <v>6788497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2557,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,37 +2589,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R20" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2663,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,43 +2696,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R21" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126980992</v>
+        <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466938</v>
+        <v>467170</v>
       </c>
       <c r="R23" t="n">
-        <v>6788495</v>
+        <v>6788379</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,43 +3014,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126981093</v>
+        <v>126980992</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3058,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467036</v>
+        <v>466938</v>
       </c>
       <c r="R24" t="n">
-        <v>6788544</v>
+        <v>6788495</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3094,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,37 +3120,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126982133</v>
+        <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467170</v>
+        <v>467036</v>
       </c>
       <c r="R25" t="n">
-        <v>6788379</v>
+        <v>6788544</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126982407</v>
+        <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467069</v>
+        <v>467169</v>
       </c>
       <c r="R26" t="n">
-        <v>6788429</v>
+        <v>6788515</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126981421</v>
+        <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467286</v>
+        <v>467030</v>
       </c>
       <c r="R27" t="n">
-        <v>6788495</v>
+        <v>6788581</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126980828</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466997</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788554</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982583</v>
+        <v>126981348</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467052</v>
+        <v>467266</v>
       </c>
       <c r="R31" t="n">
-        <v>6788489</v>
+        <v>6788513</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126981348</v>
+        <v>126982340</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467266</v>
+        <v>467059</v>
       </c>
       <c r="R33" t="n">
-        <v>6788513</v>
+        <v>6788254</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,10 +4076,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982340</v>
+        <v>126982583</v>
       </c>
       <c r="B34" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467059</v>
+        <v>467052</v>
       </c>
       <c r="R34" t="n">
-        <v>6788254</v>
+        <v>6788489</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4185,7 +4185,7 @@
         <v>126982209</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126981292</v>
+        <v>126980696</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,26 +4299,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467259</v>
+        <v>466966</v>
       </c>
       <c r="R36" t="n">
-        <v>6788550</v>
+        <v>6788554</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4366,7 +4371,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4380,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4394,10 +4398,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126980696</v>
+        <v>126981292</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4405,31 +4409,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4437,10 +4436,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466966</v>
+        <v>467259</v>
       </c>
       <c r="R37" t="n">
-        <v>6788554</v>
+        <v>6788550</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4477,7 +4476,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4486,6 +4485,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,43 +4610,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4654,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R39" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4690,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,37 +4716,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R40" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4791,11 +4796,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R41" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R42" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,37 +888,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R4" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,43 +995,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R5" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
         <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>126981689</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>80074</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,37 +1738,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982112</v>
+        <v>126982469</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467212</v>
+        <v>467023</v>
       </c>
       <c r="R12" t="n">
-        <v>6788366</v>
+        <v>6788417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B13" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R13" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,43 +1951,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126982469</v>
+        <v>126980881</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>91343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467023</v>
+        <v>467015</v>
       </c>
       <c r="R14" t="n">
-        <v>6788417</v>
+        <v>6788576</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,7 +2060,7 @@
         <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,43 +2589,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2633,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R20" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2669,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,37 +2695,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R21" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2770,11 +2775,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,37 +2908,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126982133</v>
+        <v>126981093</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2946,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467170</v>
+        <v>467036</v>
       </c>
       <c r="R23" t="n">
-        <v>6788379</v>
+        <v>6788544</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2982,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126980992</v>
+        <v>126982133</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466938</v>
+        <v>467170</v>
       </c>
       <c r="R24" t="n">
-        <v>6788495</v>
+        <v>6788379</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3092,7 +3093,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,43 +3121,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126981093</v>
+        <v>126980992</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467036</v>
+        <v>466938</v>
       </c>
       <c r="R25" t="n">
-        <v>6788544</v>
+        <v>6788495</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3200,6 +3195,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R26" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126980910</v>
+        <v>126982407</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467030</v>
+        <v>467069</v>
       </c>
       <c r="R27" t="n">
-        <v>6788581</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981421</v>
+        <v>126980828</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467286</v>
+        <v>466997</v>
       </c>
       <c r="R28" t="n">
-        <v>6788495</v>
+        <v>6788554</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126982407</v>
+        <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467069</v>
+        <v>467169</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788515</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980828</v>
+        <v>126980910</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466997</v>
+        <v>467030</v>
       </c>
       <c r="R30" t="n">
-        <v>6788554</v>
+        <v>6788581</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,7 +3760,7 @@
         <v>126981348</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,43 +3863,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981156</v>
+        <v>126982583</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3907,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467056</v>
+        <v>467052</v>
       </c>
       <c r="R32" t="n">
-        <v>6788601</v>
+        <v>6788489</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3943,6 +3937,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982340</v>
+        <v>126982209</v>
       </c>
       <c r="B33" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467059</v>
+        <v>467185</v>
       </c>
       <c r="R33" t="n">
-        <v>6788254</v>
+        <v>6788310</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,37 +4075,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982583</v>
+        <v>126981156</v>
       </c>
       <c r="B34" t="n">
-        <v>79629</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467052</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6788489</v>
+        <v>6788601</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4150,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982209</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467185</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788310</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,7 +4401,7 @@
         <v>126981292</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1738,43 +1738,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982469</v>
+        <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467023</v>
+        <v>467212</v>
       </c>
       <c r="R12" t="n">
-        <v>6788417</v>
+        <v>6788366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1818,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126982112</v>
+        <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467212</v>
+        <v>467015</v>
       </c>
       <c r="R13" t="n">
-        <v>6788366</v>
+        <v>6788576</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,37 +1950,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126980881</v>
+        <v>126982469</v>
       </c>
       <c r="B14" t="n">
-        <v>91343</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467015</v>
+        <v>467023</v>
       </c>
       <c r="R14" t="n">
-        <v>6788576</v>
+        <v>6788417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2908,43 +2908,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126981093</v>
+        <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2952,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467036</v>
+        <v>467170</v>
       </c>
       <c r="R23" t="n">
-        <v>6788544</v>
+        <v>6788379</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2988,6 +2982,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126982133</v>
+        <v>126980992</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3053,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467170</v>
+        <v>466938</v>
       </c>
       <c r="R24" t="n">
-        <v>6788379</v>
+        <v>6788495</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,37 +3120,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126980992</v>
+        <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466938</v>
+        <v>467036</v>
       </c>
       <c r="R25" t="n">
-        <v>6788495</v>
+        <v>6788544</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981421</v>
+        <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467286</v>
+        <v>467169</v>
       </c>
       <c r="R26" t="n">
-        <v>6788495</v>
+        <v>6788515</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126982407</v>
+        <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467069</v>
+        <v>467030</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788581</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980828</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466997</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788554</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981498</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467169</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788515</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,37 +3757,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981348</v>
+        <v>126981156</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3795,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467266</v>
+        <v>467056</v>
       </c>
       <c r="R31" t="n">
-        <v>6788513</v>
+        <v>6788601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3831,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126982583</v>
+        <v>126982340</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3874,21 +3875,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3901,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467052</v>
+        <v>467059</v>
       </c>
       <c r="R32" t="n">
-        <v>6788489</v>
+        <v>6788254</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3969,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982209</v>
+        <v>126981348</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467185</v>
+        <v>467266</v>
       </c>
       <c r="R33" t="n">
-        <v>6788310</v>
+        <v>6788513</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4048,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,43 +4076,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981156</v>
+        <v>126982583</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467052</v>
       </c>
       <c r="R34" t="n">
-        <v>6788601</v>
+        <v>6788489</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4155,6 +4150,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126982209</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467185</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788310</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2908,37 +2908,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126982133</v>
+        <v>126981093</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2946,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467170</v>
+        <v>467036</v>
       </c>
       <c r="R23" t="n">
-        <v>6788379</v>
+        <v>6788544</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2982,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126980992</v>
+        <v>126982133</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3052,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466938</v>
+        <v>467170</v>
       </c>
       <c r="R24" t="n">
-        <v>6788495</v>
+        <v>6788379</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3092,7 +3093,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,43 +3121,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126981093</v>
+        <v>126980992</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467036</v>
+        <v>466938</v>
       </c>
       <c r="R25" t="n">
-        <v>6788544</v>
+        <v>6788495</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3200,6 +3195,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R26" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126980910</v>
+        <v>126982407</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467030</v>
+        <v>467069</v>
       </c>
       <c r="R27" t="n">
-        <v>6788581</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981421</v>
+        <v>126980828</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467286</v>
+        <v>466997</v>
       </c>
       <c r="R28" t="n">
-        <v>6788495</v>
+        <v>6788554</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126982407</v>
+        <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467069</v>
+        <v>467169</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788515</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980828</v>
+        <v>126980910</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466997</v>
+        <v>467030</v>
       </c>
       <c r="R30" t="n">
-        <v>6788554</v>
+        <v>6788581</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,43 +888,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R4" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,37 +994,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R5" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981259</v>
+        <v>126981243</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467232</v>
+        <v>467205</v>
       </c>
       <c r="R9" t="n">
-        <v>6788583</v>
+        <v>6788649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981689</v>
+        <v>126981259</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467264</v>
+        <v>467232</v>
       </c>
       <c r="R10" t="n">
-        <v>6788324</v>
+        <v>6788583</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,32 +1632,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981243</v>
+        <v>126981689</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467205</v>
+        <v>467264</v>
       </c>
       <c r="R11" t="n">
-        <v>6788649</v>
+        <v>6788324</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,7 +1847,7 @@
         <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2270,37 +2270,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126982391</v>
+        <v>126980955</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2308,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467048</v>
+        <v>466936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788349</v>
+        <v>6788497</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2344,11 +2350,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126981571</v>
+        <v>126982391</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2414,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467237</v>
+        <v>467048</v>
       </c>
       <c r="R18" t="n">
-        <v>6788467</v>
+        <v>6788349</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,43 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126980955</v>
+        <v>126981571</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466936</v>
+        <v>467237</v>
       </c>
       <c r="R19" t="n">
-        <v>6788497</v>
+        <v>6788467</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2562,6 +2557,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2908,43 +2908,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126981093</v>
+        <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2952,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467036</v>
+        <v>467170</v>
       </c>
       <c r="R23" t="n">
-        <v>6788544</v>
+        <v>6788379</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2988,6 +2982,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126982133</v>
+        <v>126980992</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3053,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467170</v>
+        <v>466938</v>
       </c>
       <c r="R24" t="n">
-        <v>6788379</v>
+        <v>6788495</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,37 +3120,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126980992</v>
+        <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466938</v>
+        <v>467036</v>
       </c>
       <c r="R25" t="n">
-        <v>6788495</v>
+        <v>6788544</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981421</v>
+        <v>126982407</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467286</v>
+        <v>467069</v>
       </c>
       <c r="R26" t="n">
-        <v>6788495</v>
+        <v>6788429</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126982407</v>
+        <v>126980828</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467069</v>
+        <v>466997</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788554</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980828</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466997</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788554</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3757,43 +3757,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981156</v>
+        <v>126982209</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467056</v>
+        <v>467185</v>
       </c>
       <c r="R31" t="n">
-        <v>6788601</v>
+        <v>6788310</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3837,6 +3831,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,10 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126982340</v>
+        <v>126981348</v>
       </c>
       <c r="B32" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,21 +3874,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467059</v>
+        <v>467266</v>
       </c>
       <c r="R32" t="n">
-        <v>6788254</v>
+        <v>6788513</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3942,7 +3941,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,7 +3969,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126981348</v>
+        <v>126982583</v>
       </c>
       <c r="B33" t="n">
         <v>79632</v>
@@ -4008,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467266</v>
+        <v>467052</v>
       </c>
       <c r="R33" t="n">
-        <v>6788513</v>
+        <v>6788489</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,37 +4075,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982583</v>
+        <v>126981156</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467052</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6788489</v>
+        <v>6788601</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4150,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982209</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467185</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788310</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126980696</v>
+        <v>126981604</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,31 +4299,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4331,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466966</v>
+        <v>467289</v>
       </c>
       <c r="R36" t="n">
-        <v>6788554</v>
+        <v>6788427</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4371,7 +4366,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,6 +4375,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4398,10 +4394,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126981292</v>
+        <v>126980696</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4409,26 +4405,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4436,10 +4437,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467259</v>
+        <v>466966</v>
       </c>
       <c r="R37" t="n">
-        <v>6788550</v>
+        <v>6788554</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4476,7 +4477,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,7 +4486,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126981604</v>
+        <v>126981292</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467289</v>
+        <v>467259</v>
       </c>
       <c r="R38" t="n">
-        <v>6788427</v>
+        <v>6788550</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4610,37 +4610,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4648,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R39" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4684,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,43 +4717,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4760,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R40" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4796,6 +4791,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R41" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B42" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R42" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126982281</v>
+        <v>126981219</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467099</v>
+        <v>467207</v>
       </c>
       <c r="R6" t="n">
-        <v>6788291</v>
+        <v>6788653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126981219</v>
+        <v>126982281</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467207</v>
+        <v>467099</v>
       </c>
       <c r="R7" t="n">
-        <v>6788653</v>
+        <v>6788291</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981243</v>
+        <v>126981689</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467205</v>
+        <v>467264</v>
       </c>
       <c r="R9" t="n">
-        <v>6788649</v>
+        <v>6788324</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981259</v>
+        <v>126981243</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467232</v>
+        <v>467205</v>
       </c>
       <c r="R10" t="n">
-        <v>6788583</v>
+        <v>6788649</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981689</v>
+        <v>126981259</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467264</v>
+        <v>467232</v>
       </c>
       <c r="R11" t="n">
-        <v>6788324</v>
+        <v>6788583</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2270,43 +2270,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126980955</v>
+        <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2314,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466936</v>
+        <v>467048</v>
       </c>
       <c r="R17" t="n">
-        <v>6788497</v>
+        <v>6788349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126982391</v>
+        <v>126981571</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2415,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467048</v>
+        <v>467237</v>
       </c>
       <c r="R18" t="n">
-        <v>6788349</v>
+        <v>6788467</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2455,7 +2454,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,37 +2482,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126981571</v>
+        <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467237</v>
+        <v>466936</v>
       </c>
       <c r="R19" t="n">
-        <v>6788467</v>
+        <v>6788497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2557,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3227,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126982407</v>
+        <v>126981421</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467069</v>
+        <v>467286</v>
       </c>
       <c r="R26" t="n">
-        <v>6788429</v>
+        <v>6788495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126980828</v>
+        <v>126981498</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466997</v>
+        <v>467169</v>
       </c>
       <c r="R27" t="n">
-        <v>6788554</v>
+        <v>6788515</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981421</v>
+        <v>126980910</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467286</v>
+        <v>467030</v>
       </c>
       <c r="R28" t="n">
-        <v>6788495</v>
+        <v>6788581</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981498</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467169</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788515</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4610,43 +4610,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4654,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R39" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4690,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,37 +4716,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R40" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4791,11 +4796,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,37 +888,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R4" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,43 +995,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R5" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981689</v>
+        <v>126981243</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467264</v>
+        <v>467205</v>
       </c>
       <c r="R9" t="n">
-        <v>6788324</v>
+        <v>6788649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981243</v>
+        <v>126981259</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467205</v>
+        <v>467232</v>
       </c>
       <c r="R10" t="n">
-        <v>6788649</v>
+        <v>6788583</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981259</v>
+        <v>126981689</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467232</v>
+        <v>467264</v>
       </c>
       <c r="R11" t="n">
-        <v>6788583</v>
+        <v>6788324</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2589,37 +2589,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R20" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2663,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,43 +2696,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R21" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126981498</v>
+        <v>126982407</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467169</v>
+        <v>467069</v>
       </c>
       <c r="R27" t="n">
-        <v>6788515</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980910</v>
+        <v>126980828</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467030</v>
+        <v>466997</v>
       </c>
       <c r="R28" t="n">
-        <v>6788581</v>
+        <v>6788554</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126982407</v>
+        <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467069</v>
+        <v>467169</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788515</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980828</v>
+        <v>126980910</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466997</v>
+        <v>467030</v>
       </c>
       <c r="R30" t="n">
-        <v>6788554</v>
+        <v>6788581</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982209</v>
+        <v>126981348</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467185</v>
+        <v>467266</v>
       </c>
       <c r="R31" t="n">
-        <v>6788310</v>
+        <v>6788513</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,7 +3863,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981348</v>
+        <v>126982583</v>
       </c>
       <c r="B32" t="n">
         <v>79632</v>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467266</v>
+        <v>467052</v>
       </c>
       <c r="R32" t="n">
-        <v>6788513</v>
+        <v>6788489</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982583</v>
+        <v>126982340</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467052</v>
+        <v>467059</v>
       </c>
       <c r="R33" t="n">
-        <v>6788489</v>
+        <v>6788254</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4075,43 +4075,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981156</v>
+        <v>126982209</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4119,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467185</v>
       </c>
       <c r="R34" t="n">
-        <v>6788601</v>
+        <v>6788310</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4155,6 +4149,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,37 +4181,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126981156</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467056</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788601</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4256,11 +4261,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,7 +4288,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126981604</v>
+        <v>126981292</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467289</v>
+        <v>467259</v>
       </c>
       <c r="R36" t="n">
-        <v>6788427</v>
+        <v>6788550</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4394,10 +4394,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126980696</v>
+        <v>126981604</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4405,31 +4405,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466966</v>
+        <v>467289</v>
       </c>
       <c r="R37" t="n">
-        <v>6788554</v>
+        <v>6788427</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4477,7 +4472,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4486,6 +4481,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4504,10 +4500,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126981292</v>
+        <v>126980696</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4515,26 +4511,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4542,10 +4543,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467259</v>
+        <v>466966</v>
       </c>
       <c r="R38" t="n">
-        <v>6788550</v>
+        <v>6788554</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,7 +4592,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,43 +888,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R4" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,37 +994,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R5" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126981219</v>
+        <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467207</v>
+        <v>467099</v>
       </c>
       <c r="R6" t="n">
-        <v>6788653</v>
+        <v>6788291</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126982281</v>
+        <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467099</v>
+        <v>467207</v>
       </c>
       <c r="R7" t="n">
-        <v>6788291</v>
+        <v>6788653</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1738,37 +1738,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982112</v>
+        <v>126982469</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467212</v>
+        <v>467023</v>
       </c>
       <c r="R12" t="n">
-        <v>6788366</v>
+        <v>6788417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R13" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,43 +1951,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126982469</v>
+        <v>126980881</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>91344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467023</v>
+        <v>467015</v>
       </c>
       <c r="R14" t="n">
-        <v>6788417</v>
+        <v>6788576</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982340</v>
+        <v>126982209</v>
       </c>
       <c r="B33" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467059</v>
+        <v>467185</v>
       </c>
       <c r="R33" t="n">
-        <v>6788254</v>
+        <v>6788310</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,37 +4075,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982209</v>
+        <v>126981156</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4113,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467185</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6788310</v>
+        <v>6788601</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4149,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,43 +4182,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4261,6 +4256,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -1738,43 +1738,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982469</v>
+        <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467023</v>
+        <v>467212</v>
       </c>
       <c r="R12" t="n">
-        <v>6788417</v>
+        <v>6788366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1818,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126982112</v>
+        <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467212</v>
+        <v>467015</v>
       </c>
       <c r="R13" t="n">
-        <v>6788366</v>
+        <v>6788576</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,37 +1950,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126980881</v>
+        <v>126982469</v>
       </c>
       <c r="B14" t="n">
-        <v>91344</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467015</v>
+        <v>467023</v>
       </c>
       <c r="R14" t="n">
-        <v>6788576</v>
+        <v>6788417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,37 +2270,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126982391</v>
+        <v>126980955</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2308,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467048</v>
+        <v>466936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788349</v>
+        <v>6788497</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2344,11 +2350,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126981571</v>
+        <v>126982391</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2414,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467237</v>
+        <v>467048</v>
       </c>
       <c r="R18" t="n">
-        <v>6788467</v>
+        <v>6788349</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,43 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126980955</v>
+        <v>126981571</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466936</v>
+        <v>467237</v>
       </c>
       <c r="R19" t="n">
-        <v>6788497</v>
+        <v>6788467</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2562,6 +2557,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981421</v>
+        <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467286</v>
+        <v>467169</v>
       </c>
       <c r="R26" t="n">
-        <v>6788495</v>
+        <v>6788515</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126982407</v>
+        <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467069</v>
+        <v>467030</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788581</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980828</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466997</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788554</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981498</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467169</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788515</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,37 +888,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R4" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,43 +995,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R5" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
         <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>126981527</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981243</v>
+        <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467205</v>
+        <v>467232</v>
       </c>
       <c r="R9" t="n">
-        <v>6788649</v>
+        <v>6788583</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981259</v>
+        <v>126981689</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467232</v>
+        <v>467264</v>
       </c>
       <c r="R10" t="n">
-        <v>6788583</v>
+        <v>6788324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,32 +1632,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981689</v>
+        <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>80081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467264</v>
+        <v>467205</v>
       </c>
       <c r="R11" t="n">
-        <v>6788324</v>
+        <v>6788649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,7 +1741,7 @@
         <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>126982469</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,43 +2270,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126980955</v>
+        <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2314,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466936</v>
+        <v>467048</v>
       </c>
       <c r="R17" t="n">
-        <v>6788497</v>
+        <v>6788349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126982391</v>
+        <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467048</v>
+        <v>467237</v>
       </c>
       <c r="R18" t="n">
-        <v>6788349</v>
+        <v>6788467</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2455,7 +2454,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,37 +2482,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126981571</v>
+        <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467237</v>
+        <v>466936</v>
       </c>
       <c r="R19" t="n">
-        <v>6788467</v>
+        <v>6788497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2557,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,7 +2592,7 @@
         <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>126980992</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R26" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126980910</v>
+        <v>126982407</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467030</v>
+        <v>467069</v>
       </c>
       <c r="R27" t="n">
-        <v>6788581</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981421</v>
+        <v>126980828</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467286</v>
+        <v>466997</v>
       </c>
       <c r="R28" t="n">
-        <v>6788495</v>
+        <v>6788554</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126982407</v>
+        <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467069</v>
+        <v>467169</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788515</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980828</v>
+        <v>126980910</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466997</v>
+        <v>467030</v>
       </c>
       <c r="R30" t="n">
-        <v>6788554</v>
+        <v>6788581</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981348</v>
+        <v>126982340</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467266</v>
+        <v>467059</v>
       </c>
       <c r="R31" t="n">
-        <v>6788513</v>
+        <v>6788254</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,10 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126982583</v>
+        <v>126981348</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467052</v>
+        <v>467266</v>
       </c>
       <c r="R32" t="n">
-        <v>6788489</v>
+        <v>6788513</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982209</v>
+        <v>126982583</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467185</v>
+        <v>467052</v>
       </c>
       <c r="R33" t="n">
-        <v>6788310</v>
+        <v>6788489</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,43 +4075,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981156</v>
+        <v>126982209</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4119,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467185</v>
       </c>
       <c r="R34" t="n">
-        <v>6788601</v>
+        <v>6788310</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4155,6 +4149,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,37 +4181,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126981156</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467056</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788601</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4256,11 +4261,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4291,7 @@
         <v>126981292</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>126981604</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>126980696</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R41" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R42" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2589,43 +2589,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2633,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R20" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2669,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,37 +2695,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R21" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2770,11 +2775,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981421</v>
+        <v>126980910</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467286</v>
+        <v>467030</v>
       </c>
       <c r="R26" t="n">
-        <v>6788495</v>
+        <v>6788581</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126982407</v>
+        <v>126981421</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467069</v>
+        <v>467286</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788495</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980828</v>
+        <v>126982407</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466997</v>
+        <v>467069</v>
       </c>
       <c r="R28" t="n">
-        <v>6788554</v>
+        <v>6788429</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981498</v>
+        <v>126980828</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467169</v>
+        <v>466997</v>
       </c>
       <c r="R29" t="n">
-        <v>6788515</v>
+        <v>6788554</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126981498</v>
       </c>
       <c r="B30" t="n">
         <v>78777</v>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>467169</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788515</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3757,37 +3757,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982340</v>
+        <v>126981156</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3795,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467059</v>
+        <v>467056</v>
       </c>
       <c r="R31" t="n">
-        <v>6788254</v>
+        <v>6788601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3831,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4181,43 +4182,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4261,6 +4256,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4610,37 +4610,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4648,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R39" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4684,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,43 +4717,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4760,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R40" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4796,6 +4791,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -1738,37 +1738,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982112</v>
+        <v>126982469</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467212</v>
+        <v>467023</v>
       </c>
       <c r="R12" t="n">
-        <v>6788366</v>
+        <v>6788417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R13" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,43 +1951,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126982469</v>
+        <v>126980881</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467023</v>
+        <v>467015</v>
       </c>
       <c r="R14" t="n">
-        <v>6788417</v>
+        <v>6788576</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126981421</v>
+        <v>126981498</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467286</v>
+        <v>467169</v>
       </c>
       <c r="R27" t="n">
-        <v>6788495</v>
+        <v>6788515</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126982407</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467069</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788429</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,7 +3545,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126980828</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466997</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788554</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126981498</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467169</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788515</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4610,43 +4610,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4654,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R39" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4690,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,37 +4716,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R40" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4791,11 +4796,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R27" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126981421</v>
+        <v>126982407</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467286</v>
+        <v>467069</v>
       </c>
       <c r="R28" t="n">
-        <v>6788495</v>
+        <v>6788429</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,7 +3545,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126982407</v>
+        <v>126980828</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467069</v>
+        <v>466997</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788554</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980828</v>
+        <v>126981498</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466997</v>
+        <v>467169</v>
       </c>
       <c r="R30" t="n">
-        <v>6788554</v>
+        <v>6788515</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,43 +3757,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R31" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3837,6 +3831,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,37 +4181,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126981156</v>
       </c>
       <c r="B35" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467056</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788601</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4256,11 +4261,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126981292</v>
+        <v>126980696</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,26 +4299,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467259</v>
+        <v>466966</v>
       </c>
       <c r="R36" t="n">
-        <v>6788550</v>
+        <v>6788554</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4366,7 +4371,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4380,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4394,7 +4398,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126981604</v>
+        <v>126981292</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4432,10 +4436,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467289</v>
+        <v>467259</v>
       </c>
       <c r="R37" t="n">
-        <v>6788427</v>
+        <v>6788550</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4472,7 +4476,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4500,10 +4504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126980696</v>
+        <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4511,31 +4515,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4543,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466966</v>
+        <v>467289</v>
       </c>
       <c r="R38" t="n">
-        <v>6788554</v>
+        <v>6788427</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4583,7 +4582,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,6 +4591,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R41" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B42" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R42" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,37 +2270,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126982391</v>
+        <v>126980955</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2308,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467048</v>
+        <v>466936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788349</v>
+        <v>6788497</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2344,11 +2350,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126981571</v>
+        <v>126982391</v>
       </c>
       <c r="B18" t="n">
         <v>79018</v>
@@ -2414,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467237</v>
+        <v>467048</v>
       </c>
       <c r="R18" t="n">
-        <v>6788467</v>
+        <v>6788349</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,43 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126980955</v>
+        <v>126981571</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466936</v>
+        <v>467237</v>
       </c>
       <c r="R19" t="n">
-        <v>6788497</v>
+        <v>6788467</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2562,6 +2557,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,37 +2589,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R20" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2663,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,43 +2696,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R21" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126980910</v>
+        <v>126981421</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467030</v>
+        <v>467286</v>
       </c>
       <c r="R26" t="n">
-        <v>6788581</v>
+        <v>6788495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126981421</v>
+        <v>126982407</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467286</v>
+        <v>467069</v>
       </c>
       <c r="R27" t="n">
-        <v>6788495</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126982407</v>
+        <v>126980828</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467069</v>
+        <v>466997</v>
       </c>
       <c r="R28" t="n">
-        <v>6788429</v>
+        <v>6788554</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126980828</v>
+        <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466997</v>
+        <v>467169</v>
       </c>
       <c r="R29" t="n">
-        <v>6788554</v>
+        <v>6788515</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126981498</v>
+        <v>126980910</v>
       </c>
       <c r="B30" t="n">
         <v>78777</v>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467169</v>
+        <v>467030</v>
       </c>
       <c r="R30" t="n">
-        <v>6788515</v>
+        <v>6788581</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982340</v>
+        <v>126982209</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467059</v>
+        <v>467185</v>
       </c>
       <c r="R31" t="n">
-        <v>6788254</v>
+        <v>6788310</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4075,37 +4075,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982209</v>
+        <v>126981156</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4113,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467185</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6788310</v>
+        <v>6788601</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4149,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,43 +4182,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4261,6 +4256,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126980696</v>
+        <v>126981292</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,31 +4299,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4331,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466966</v>
+        <v>467259</v>
       </c>
       <c r="R36" t="n">
-        <v>6788554</v>
+        <v>6788550</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4371,7 +4366,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,6 +4375,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4398,7 +4394,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126981292</v>
+        <v>126981604</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4436,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467259</v>
+        <v>467289</v>
       </c>
       <c r="R37" t="n">
-        <v>6788550</v>
+        <v>6788427</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4476,7 +4472,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4504,10 +4500,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126981604</v>
+        <v>126980696</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4515,26 +4511,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4542,10 +4543,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467289</v>
+        <v>466966</v>
       </c>
       <c r="R38" t="n">
-        <v>6788427</v>
+        <v>6788554</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,7 +4592,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R41" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R42" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126982281</v>
+        <v>126981219</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467099</v>
+        <v>467207</v>
       </c>
       <c r="R6" t="n">
-        <v>6788291</v>
+        <v>6788653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126981219</v>
+        <v>126982281</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467207</v>
+        <v>467099</v>
       </c>
       <c r="R7" t="n">
-        <v>6788653</v>
+        <v>6788291</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,43 +2270,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126980955</v>
+        <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2314,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466936</v>
+        <v>467048</v>
       </c>
       <c r="R17" t="n">
-        <v>6788497</v>
+        <v>6788349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126982391</v>
+        <v>126981571</v>
       </c>
       <c r="B18" t="n">
         <v>79018</v>
@@ -2415,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467048</v>
+        <v>467237</v>
       </c>
       <c r="R18" t="n">
-        <v>6788349</v>
+        <v>6788467</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2455,7 +2454,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,37 +2482,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126981571</v>
+        <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467237</v>
+        <v>466936</v>
       </c>
       <c r="R19" t="n">
-        <v>6788467</v>
+        <v>6788497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2557,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,43 +2589,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2633,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R20" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2669,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,37 +2695,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R21" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2770,11 +2775,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3757,37 +3757,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982209</v>
+        <v>126981156</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3795,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467185</v>
+        <v>467056</v>
       </c>
       <c r="R31" t="n">
-        <v>6788310</v>
+        <v>6788601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3831,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981348</v>
+        <v>126982340</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3874,21 +3875,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3901,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467266</v>
+        <v>467059</v>
       </c>
       <c r="R32" t="n">
-        <v>6788513</v>
+        <v>6788254</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3941,7 +3942,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982583</v>
+        <v>126982209</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467052</v>
+        <v>467185</v>
       </c>
       <c r="R33" t="n">
-        <v>6788489</v>
+        <v>6788310</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4048,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,43 +4076,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981156</v>
+        <v>126981348</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467266</v>
       </c>
       <c r="R34" t="n">
-        <v>6788601</v>
+        <v>6788513</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4155,6 +4150,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126982583</v>
       </c>
       <c r="B35" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467052</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788489</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4610,37 +4610,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4648,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R39" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4684,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,43 +4717,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4760,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R40" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4796,6 +4791,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -998,7 +998,7 @@
         <v>126982560</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126981219</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126982281</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981259</v>
+        <v>126981243</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467232</v>
+        <v>467205</v>
       </c>
       <c r="R9" t="n">
-        <v>6788583</v>
+        <v>6788649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981689</v>
+        <v>126981259</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467264</v>
+        <v>467232</v>
       </c>
       <c r="R10" t="n">
-        <v>6788324</v>
+        <v>6788583</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,32 +1632,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981243</v>
+        <v>126981689</v>
       </c>
       <c r="B11" t="n">
-        <v>80081</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467205</v>
+        <v>467264</v>
       </c>
       <c r="R11" t="n">
-        <v>6788649</v>
+        <v>6788324</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,43 +1738,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982469</v>
+        <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467023</v>
+        <v>467212</v>
       </c>
       <c r="R12" t="n">
-        <v>6788417</v>
+        <v>6788366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1818,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126982112</v>
+        <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467212</v>
+        <v>467015</v>
       </c>
       <c r="R13" t="n">
-        <v>6788366</v>
+        <v>6788576</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,37 +1950,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126980881</v>
+        <v>126982469</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467015</v>
+        <v>467023</v>
       </c>
       <c r="R14" t="n">
-        <v>6788576</v>
+        <v>6788417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,7 +2167,7 @@
         <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>126981466</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>126980992</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>126981421</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>126982407</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>126980828</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126981498</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>126980910</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,43 +3757,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R31" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3837,6 +3831,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,10 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126982340</v>
+        <v>126981348</v>
       </c>
       <c r="B32" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,21 +3874,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467059</v>
+        <v>467266</v>
       </c>
       <c r="R32" t="n">
-        <v>6788254</v>
+        <v>6788513</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3942,7 +3941,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982209</v>
+        <v>126982583</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467185</v>
+        <v>467052</v>
       </c>
       <c r="R33" t="n">
-        <v>6788310</v>
+        <v>6788489</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4048,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981348</v>
+        <v>126982209</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,21 +4086,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467266</v>
+        <v>467185</v>
       </c>
       <c r="R34" t="n">
-        <v>6788513</v>
+        <v>6788310</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4154,7 +4153,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,37 +4181,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982583</v>
+        <v>126981156</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467052</v>
+        <v>467056</v>
       </c>
       <c r="R35" t="n">
-        <v>6788489</v>
+        <v>6788601</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4256,11 +4261,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4291,7 @@
         <v>126981292</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>126981604</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>126980696</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,43 +4610,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4654,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R39" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4690,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,37 +4716,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R40" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4791,11 +4796,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4826,7 +4826,7 @@
         <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126981243</v>
+        <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467205</v>
+        <v>467232</v>
       </c>
       <c r="R9" t="n">
-        <v>6788649</v>
+        <v>6788583</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en sälg</t>
+          <t>Sparsamt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126981259</v>
+        <v>126981689</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467232</v>
+        <v>467264</v>
       </c>
       <c r="R10" t="n">
-        <v>6788583</v>
+        <v>6788324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,32 +1632,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126981689</v>
+        <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467264</v>
+        <v>467205</v>
       </c>
       <c r="R11" t="n">
-        <v>6788324</v>
+        <v>6788649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,37 +2270,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126982391</v>
+        <v>126980955</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2308,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467048</v>
+        <v>466936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788349</v>
+        <v>6788497</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2344,11 +2350,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126981571</v>
+        <v>126982391</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2414,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467237</v>
+        <v>467048</v>
       </c>
       <c r="R18" t="n">
-        <v>6788467</v>
+        <v>6788349</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,43 +2483,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126980955</v>
+        <v>126981571</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466936</v>
+        <v>467237</v>
       </c>
       <c r="R19" t="n">
-        <v>6788497</v>
+        <v>6788467</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2562,6 +2557,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,37 +2589,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R20" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2663,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,43 +2696,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R21" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,37 +2908,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126982133</v>
+        <v>126981093</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2946,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467170</v>
+        <v>467036</v>
       </c>
       <c r="R23" t="n">
-        <v>6788379</v>
+        <v>6788544</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2982,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126980992</v>
+        <v>126982133</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -3052,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466938</v>
+        <v>467170</v>
       </c>
       <c r="R24" t="n">
-        <v>6788495</v>
+        <v>6788379</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3092,7 +3093,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,43 +3121,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126981093</v>
+        <v>126980992</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467036</v>
+        <v>466938</v>
       </c>
       <c r="R25" t="n">
-        <v>6788544</v>
+        <v>6788495</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3200,6 +3195,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126981421</v>
+        <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467286</v>
+        <v>467169</v>
       </c>
       <c r="R26" t="n">
-        <v>6788495</v>
+        <v>6788515</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126982407</v>
+        <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467069</v>
+        <v>467030</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788581</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,10 +3545,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981498</v>
+        <v>126981421</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467169</v>
+        <v>467286</v>
       </c>
       <c r="R29" t="n">
-        <v>6788515</v>
+        <v>6788495</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126980910</v>
+        <v>126982407</v>
       </c>
       <c r="B30" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467030</v>
+        <v>467069</v>
       </c>
       <c r="R30" t="n">
-        <v>6788581</v>
+        <v>6788429</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126982340</v>
+        <v>126981348</v>
       </c>
       <c r="B31" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467059</v>
+        <v>467266</v>
       </c>
       <c r="R31" t="n">
-        <v>6788254</v>
+        <v>6788513</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,7 +3863,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981348</v>
+        <v>126982583</v>
       </c>
       <c r="B32" t="n">
         <v>79638</v>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467266</v>
+        <v>467052</v>
       </c>
       <c r="R32" t="n">
-        <v>6788513</v>
+        <v>6788489</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982583</v>
+        <v>126982209</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467052</v>
+        <v>467185</v>
       </c>
       <c r="R33" t="n">
-        <v>6788489</v>
+        <v>6788310</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,37 +4075,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982209</v>
+        <v>126981156</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4113,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467185</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6788310</v>
+        <v>6788601</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4149,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,43 +4182,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126981156</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467056</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788601</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4261,6 +4256,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4610,37 +4610,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4648,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R39" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4684,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,43 +4717,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4760,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R40" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4796,6 +4791,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R41" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B42" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R42" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2589,43 +2589,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2633,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R20" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2669,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,37 +2695,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R21" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2770,11 +2775,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,43 +2908,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126981093</v>
+        <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2952,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467036</v>
+        <v>467170</v>
       </c>
       <c r="R23" t="n">
-        <v>6788544</v>
+        <v>6788379</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2988,6 +2982,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126982133</v>
+        <v>126980992</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -3053,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467170</v>
+        <v>466938</v>
       </c>
       <c r="R24" t="n">
-        <v>6788379</v>
+        <v>6788495</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,37 +3120,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126980992</v>
+        <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466938</v>
+        <v>467036</v>
       </c>
       <c r="R25" t="n">
-        <v>6788495</v>
+        <v>6788544</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126981219</v>
+        <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467207</v>
+        <v>467099</v>
       </c>
       <c r="R6" t="n">
-        <v>6788653</v>
+        <v>6788291</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt till rikligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126982281</v>
+        <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467099</v>
+        <v>467207</v>
       </c>
       <c r="R7" t="n">
-        <v>6788291</v>
+        <v>6788653</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie 50m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1738,37 +1738,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982112</v>
+        <v>126982469</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467212</v>
+        <v>467023</v>
       </c>
       <c r="R12" t="n">
-        <v>6788366</v>
+        <v>6788417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R13" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,43 +1951,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126982469</v>
+        <v>126980881</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467023</v>
+        <v>467015</v>
       </c>
       <c r="R14" t="n">
-        <v>6788417</v>
+        <v>6788576</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,43 +2270,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126980955</v>
+        <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2314,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466936</v>
+        <v>467048</v>
       </c>
       <c r="R17" t="n">
-        <v>6788497</v>
+        <v>6788349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126982391</v>
+        <v>126981571</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2415,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467048</v>
+        <v>467237</v>
       </c>
       <c r="R18" t="n">
-        <v>6788349</v>
+        <v>6788467</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2455,7 +2454,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,37 +2482,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126981571</v>
+        <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467237</v>
+        <v>466936</v>
       </c>
       <c r="R19" t="n">
-        <v>6788467</v>
+        <v>6788497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2557,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,37 +2589,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126981466</v>
+        <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467164</v>
+        <v>467077</v>
       </c>
       <c r="R20" t="n">
-        <v>6788512</v>
+        <v>6788529</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2663,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,43 +2696,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126982629</v>
+        <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467077</v>
+        <v>467164</v>
       </c>
       <c r="R21" t="n">
-        <v>6788529</v>
+        <v>6788512</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126980828</v>
+        <v>126981421</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466997</v>
+        <v>467286</v>
       </c>
       <c r="R28" t="n">
-        <v>6788554</v>
+        <v>6788495</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Måttligt till rkligt inom en radie 50 m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,7 +3545,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126981421</v>
+        <v>126982407</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467286</v>
+        <v>467069</v>
       </c>
       <c r="R29" t="n">
-        <v>6788495</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126982407</v>
+        <v>126980828</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467069</v>
+        <v>466997</v>
       </c>
       <c r="R30" t="n">
-        <v>6788429</v>
+        <v>6788554</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rkligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,37 +3757,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981348</v>
+        <v>126981156</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3795,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467266</v>
+        <v>467056</v>
       </c>
       <c r="R31" t="n">
-        <v>6788513</v>
+        <v>6788601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3831,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,7 +3864,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126982583</v>
+        <v>126981348</v>
       </c>
       <c r="B32" t="n">
         <v>79638</v>
@@ -3901,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467052</v>
+        <v>467266</v>
       </c>
       <c r="R32" t="n">
-        <v>6788489</v>
+        <v>6788513</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3941,7 +3942,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982209</v>
+        <v>126982583</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467185</v>
+        <v>467052</v>
       </c>
       <c r="R33" t="n">
-        <v>6788310</v>
+        <v>6788489</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4047,7 +4048,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,43 +4076,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126981156</v>
+        <v>126982209</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467185</v>
       </c>
       <c r="R34" t="n">
-        <v>6788601</v>
+        <v>6788310</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4155,6 +4150,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126981292</v>
+        <v>126980696</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,26 +4299,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467259</v>
+        <v>466966</v>
       </c>
       <c r="R36" t="n">
-        <v>6788550</v>
+        <v>6788554</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4366,7 +4371,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
+          <t>Äldre ringhack i tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4380,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4394,7 +4398,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126981604</v>
+        <v>126981292</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4432,10 +4436,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467289</v>
+        <v>467259</v>
       </c>
       <c r="R37" t="n">
-        <v>6788427</v>
+        <v>6788550</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4472,7 +4476,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50m</t>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4500,10 +4504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126980696</v>
+        <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4511,31 +4515,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4543,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466966</v>
+        <v>467289</v>
       </c>
       <c r="R38" t="n">
-        <v>6788554</v>
+        <v>6788427</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4583,7 +4582,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack i tall</t>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,6 +4591,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4610,43 +4610,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126981037</v>
+        <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4654,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>467196</v>
       </c>
       <c r="R39" t="n">
-        <v>6788502</v>
+        <v>6788658</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4690,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,37 +4716,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126981190</v>
+        <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467196</v>
+        <v>466957</v>
       </c>
       <c r="R40" t="n">
-        <v>6788658</v>
+        <v>6788502</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4791,11 +4796,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126982266</v>
+        <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467163</v>
+        <v>467043</v>
       </c>
       <c r="R41" t="n">
-        <v>6788304</v>
+        <v>6788281</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Sparsamt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126982373</v>
+        <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467043</v>
+        <v>467163</v>
       </c>
       <c r="R42" t="n">
-        <v>6788281</v>
+        <v>6788304</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Sparsamt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R2" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R3" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,43 +888,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R4" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,37 +994,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R5" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
         <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>126981527</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>126981689</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,43 +1738,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982469</v>
+        <v>126982112</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467023</v>
+        <v>467212</v>
       </c>
       <c r="R12" t="n">
-        <v>6788417</v>
+        <v>6788366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1818,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126982112</v>
+        <v>126980881</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467212</v>
+        <v>467015</v>
       </c>
       <c r="R13" t="n">
-        <v>6788366</v>
+        <v>6788576</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,37 +1950,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126980881</v>
+        <v>126982469</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467015</v>
+        <v>467023</v>
       </c>
       <c r="R14" t="n">
-        <v>6788576</v>
+        <v>6788417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,43 +2057,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R15" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2137,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2163,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2202,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R16" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2238,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>126980992</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>126981421</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,43 +3757,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981156</v>
+        <v>126981348</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467056</v>
+        <v>467266</v>
       </c>
       <c r="R31" t="n">
-        <v>6788601</v>
+        <v>6788513</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3837,6 +3831,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,37 +3863,43 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981348</v>
+        <v>126981156</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>8447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3902,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467266</v>
+        <v>467056</v>
       </c>
       <c r="R32" t="n">
-        <v>6788513</v>
+        <v>6788601</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3938,11 +3943,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982583</v>
+        <v>126982340</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467052</v>
+        <v>467059</v>
       </c>
       <c r="R33" t="n">
-        <v>6788489</v>
+        <v>6788254</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4076,10 +4076,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982209</v>
+        <v>126982583</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467185</v>
+        <v>467052</v>
       </c>
       <c r="R34" t="n">
-        <v>6788310</v>
+        <v>6788489</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982340</v>
+        <v>126982209</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467059</v>
+        <v>467185</v>
       </c>
       <c r="R35" t="n">
-        <v>6788254</v>
+        <v>6788310</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4291,7 @@
         <v>126980696</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>126981292</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29520-2025 artfynd.xlsx
+++ b/artfynd/A 29520-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126982244</v>
+        <v>126981128</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467170</v>
+        <v>467073</v>
       </c>
       <c r="R2" t="n">
-        <v>6788292</v>
+        <v>6788591</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126981128</v>
+        <v>126982244</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467073</v>
+        <v>467170</v>
       </c>
       <c r="R3" t="n">
-        <v>6788591</v>
+        <v>6788292</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom radie 50m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,37 +888,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126982560</v>
+        <v>126982355</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467052</v>
+        <v>467053</v>
       </c>
       <c r="R4" t="n">
-        <v>6788489</v>
+        <v>6788322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,43 +995,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126982355</v>
+        <v>126982560</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467053</v>
+        <v>467052</v>
       </c>
       <c r="R5" t="n">
-        <v>6788322</v>
+        <v>6788489</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
         <v>126982281</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126981219</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>126981527</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126981259</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>126981689</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126981243</v>
       </c>
       <c r="B11" t="n">
-        <v>80074</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,37 +1738,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126982112</v>
+        <v>126982469</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1776,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467212</v>
+        <v>467023</v>
       </c>
       <c r="R12" t="n">
-        <v>6788366</v>
+        <v>6788417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126980881</v>
+        <v>126982112</v>
       </c>
       <c r="B13" t="n">
-        <v>91337</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467015</v>
+        <v>467212</v>
       </c>
       <c r="R13" t="n">
-        <v>6788576</v>
+        <v>6788366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en död gran</t>
+          <t>Måttligt till rikligt inom en radie50m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,43 +1951,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126982469</v>
+        <v>126980881</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467023</v>
+        <v>467015</v>
       </c>
       <c r="R14" t="n">
-        <v>6788417</v>
+        <v>6788576</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,37 +2057,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126982527</v>
+        <v>126982167</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466985</v>
+        <v>467211</v>
       </c>
       <c r="R15" t="n">
-        <v>6788437</v>
+        <v>6788299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,43 +2164,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126982167</v>
+        <v>126982527</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467211</v>
+        <v>466985</v>
       </c>
       <c r="R16" t="n">
-        <v>6788299</v>
+        <v>6788437</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie 50m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>126982391</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>126981571</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>126980955</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>126982629</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>126981466</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126982612</v>
       </c>
       <c r="B22" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126982133</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>126980992</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126981093</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>126981498</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>126980910</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>126981421</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126982407</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>126980828</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,37 +3757,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126981348</v>
+        <v>126981156</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3795,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467266</v>
+        <v>467056</v>
       </c>
       <c r="R31" t="n">
-        <v>6788513</v>
+        <v>6788601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3831,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,43 +3864,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126981156</v>
+        <v>126981348</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3907,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467056</v>
+        <v>467266</v>
       </c>
       <c r="R32" t="n">
-        <v>6788601</v>
+        <v>6788513</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3943,6 +3938,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126982340</v>
+        <v>126982583</v>
       </c>
       <c r="B33" t="n">
-        <v>78770</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467059</v>
+        <v>467052</v>
       </c>
       <c r="R33" t="n">
-        <v>6788254</v>
+        <v>6788489</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4076,10 +4076,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126982583</v>
+        <v>126982209</v>
       </c>
       <c r="B34" t="n">
-        <v>79629</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467052</v>
+        <v>467185</v>
       </c>
       <c r="R34" t="n">
-        <v>6788489</v>
+        <v>6788310</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Måttligt inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126982209</v>
+        <v>126982340</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467185</v>
+        <v>467059</v>
       </c>
       <c r="R35" t="n">
-        <v>6788310</v>
+        <v>6788254</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Måttligt inom en radie 50 m</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4291,7 @@
         <v>126980696</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>126981292</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>126981604</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>126981190</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>126981037</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>126982373</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>126982266</v>
       </c>
       <c r="B42" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>126982503</v>
       </c>
       <c r="B43" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
